--- a/Plan/Table/TestData/12.RequestWeightData.xlsx
+++ b/Plan/Table/TestData/12.RequestWeightData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="현재_통합_문서" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\인디\FluffyDisdog\Plan\Table\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{73B71988-945A-4CF4-B81F-5E7EE0ED2AEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{06D99F8B-12AE-4560-A6F4-617DDFAC796B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="5280" windowWidth="29040" windowHeight="15720" xr2:uid="{85DF8E73-8F32-45AA-9F44-7AD32F859B3B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{1FF2AD5F-78E8-4B7B-8541-5075E3D0D6E7}"/>
   </bookViews>
   <sheets>
     <sheet name="12.RequestWeightData" sheetId="1" r:id="rId1"/>
@@ -44,13 +44,13 @@
     <t>id</t>
   </si>
   <si>
+    <t>Group_Id</t>
+  </si>
+  <si>
     <t>Card_Key</t>
   </si>
   <si>
-    <t>Box_Id</t>
-  </si>
-  <si>
-    <t>Rate</t>
+    <t>Gacha_Id</t>
   </si>
   <si>
     <t>Card_Shovel</t>
@@ -436,7 +436,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D5461BF-2F4A-4C3C-ACD9-A278CD9CEA28}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A0D2EBB-5736-4870-94C8-691A69F7EA7D}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
@@ -459,11 +459,11 @@
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
         <v>4</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
       </c>
       <c r="D2">
         <v>1</v>
